--- a/COIN_API_template.xlsx
+++ b/COIN_API_template.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -444,7 +444,16 @@
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,135 +529,165 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>gift_code_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>gift_code_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>gift1_status</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>gift2_status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>card_number</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>card_name</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>card_expiry</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>security_code</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>card_url</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>registered_at</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>07084329074</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Choai1234@</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>サトウ</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>ソウタ</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2003-11-23</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>0912</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>07092399705</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Choai1234@</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>ナカムラ</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>ハルト</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2002-02-05</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>0912</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H3" s="1" t="n"/>
-      <c r="I3" s="1" t="n"/>
-      <c r="J3" s="1" t="n"/>
-      <c r="K3" s="1" t="n"/>
-      <c r="L3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>07094342905</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Choai1234@</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>タナカ</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>ユナ</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2002-06-15</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>0912</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -661,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -678,7 +717,16 @@
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,6 +801,51 @@
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>gift_code_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>gift_code_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>gift1_status</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>gift2_status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>card_number</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>card_name</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>card_expiry</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>security_code</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>card_url</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>registered_at</t>
         </is>
@@ -772,8 +865,8 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
